--- a/data/ansp_employment.xlsx
+++ b/data/ansp_employment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05718844-0B24-4333-B3E0-E93239EBEC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F160A74-85EC-459D-97B0-14A7CAA349D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="346" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="346" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="6" r:id="rId1"/>
@@ -81,9 +81,6 @@
     <t>HungaroControl</t>
   </si>
   <si>
-    <t>IAA</t>
-  </si>
-  <si>
     <t>LFV</t>
   </si>
   <si>
@@ -181,6 +178,9 @@
   </si>
   <si>
     <t>EUROCONTROL area - average values</t>
+  </si>
+  <si>
+    <t>AirNav Ireland</t>
   </si>
 </sst>
 </file>
@@ -1384,13 +1384,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1398,32 +1398,32 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>149000</v>
+        <v>184500</v>
       </c>
       <c r="C2">
-        <v>174600</v>
+        <v>214200</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3">
-        <v>78600</v>
+        <v>92600</v>
       </c>
       <c r="C3">
-        <v>96700</v>
+        <v>111000</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4">
-        <v>101300</v>
+        <v>122900</v>
       </c>
       <c r="C4">
-        <v>122900</v>
+        <v>146500</v>
       </c>
     </row>
   </sheetData>
@@ -1438,20 +1438,21 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>38</v>
-      </c>
-      <c r="D1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1459,13 +1460,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>25157</v>
+        <v>48642</v>
       </c>
       <c r="C2">
-        <v>12004</v>
+        <v>21554</v>
       </c>
       <c r="D2">
-        <v>14278</v>
+        <v>27790</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1473,13 +1474,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>92480</v>
+        <v>198469</v>
       </c>
       <c r="C3">
-        <v>48890</v>
+        <v>79205</v>
       </c>
       <c r="D3">
-        <v>59632</v>
+        <v>107778</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1487,13 +1488,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>26608</v>
+        <v>51792</v>
       </c>
       <c r="C4">
-        <v>15573</v>
+        <v>34312</v>
       </c>
       <c r="D4">
-        <v>18564</v>
+        <v>38956</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1501,13 +1502,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>212241</v>
+        <v>267686</v>
       </c>
       <c r="C5">
-        <v>144827</v>
+        <v>182341</v>
       </c>
       <c r="D5">
-        <v>168198</v>
+        <v>213742</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1515,27 +1516,27 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>200980</v>
+        <v>187199</v>
       </c>
       <c r="C6">
-        <v>100844</v>
+        <v>116520</v>
       </c>
       <c r="D6">
-        <v>141867</v>
+        <v>152889</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7">
-        <v>33229</v>
+        <v>64772</v>
       </c>
       <c r="C7">
-        <v>27790</v>
+        <v>42073</v>
       </c>
       <c r="D7">
-        <v>29339</v>
+        <v>48367</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1543,13 +1544,13 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>97975</v>
+        <v>155130</v>
       </c>
       <c r="C8">
-        <v>43886</v>
+        <v>62556</v>
       </c>
       <c r="D8">
-        <v>57983</v>
+        <v>87175</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1557,13 +1558,13 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>114253</v>
+        <v>145458</v>
       </c>
       <c r="C9">
-        <v>55490</v>
+        <v>74829</v>
       </c>
       <c r="D9">
-        <v>75575</v>
+        <v>100709</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1571,13 +1572,13 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>103333</v>
+        <v>108233</v>
       </c>
       <c r="C10">
-        <v>65184</v>
+        <v>73413</v>
       </c>
       <c r="D10">
-        <v>82867</v>
+        <v>91027</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1585,13 +1586,13 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>259922</v>
+        <v>316618</v>
       </c>
       <c r="C11">
-        <v>108590</v>
+        <v>113654</v>
       </c>
       <c r="D11">
-        <v>154303</v>
+        <v>175360</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1599,13 +1600,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>48531</v>
+        <v>71841</v>
       </c>
       <c r="C12">
-        <v>13627</v>
+        <v>21157</v>
       </c>
       <c r="D12">
-        <v>21911</v>
+        <v>33835</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1613,13 +1614,13 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>135757</v>
+        <v>167984</v>
       </c>
       <c r="C13">
-        <v>101783</v>
+        <v>98285</v>
       </c>
       <c r="D13">
-        <v>114204</v>
+        <v>124721</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1627,27 +1628,27 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>118386</v>
+        <v>110742</v>
       </c>
       <c r="C14">
-        <v>44161</v>
+        <v>56439</v>
       </c>
       <c r="D14">
-        <v>68337</v>
+        <v>74638</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15">
-        <v>189385</v>
+        <v>214273</v>
       </c>
       <c r="C15">
-        <v>100512</v>
+        <v>119115</v>
       </c>
       <c r="D15">
-        <v>136938</v>
+        <v>157657</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1655,41 +1656,41 @@
         <v>13</v>
       </c>
       <c r="B16">
-        <v>160131</v>
+        <v>193267</v>
       </c>
       <c r="C16">
-        <v>107708</v>
+        <v>107704</v>
       </c>
       <c r="D16">
-        <v>131787</v>
+        <v>146573</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17">
-        <v>121324</v>
+        <v>122981</v>
       </c>
       <c r="C17">
-        <v>91881</v>
+        <v>83572</v>
       </c>
       <c r="D17">
-        <v>106711</v>
+        <v>102569</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18">
-        <v>79373</v>
+        <v>129617</v>
       </c>
       <c r="C18">
-        <v>56721</v>
+        <v>81951</v>
       </c>
       <c r="D18">
-        <v>64127</v>
+        <v>98098</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1697,307 +1698,307 @@
         <v>14</v>
       </c>
       <c r="B19">
-        <v>117751</v>
+        <v>143952</v>
       </c>
       <c r="C19">
-        <v>45005</v>
+        <v>65125</v>
       </c>
       <c r="D19">
-        <v>62468</v>
+        <v>85097</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B20">
-        <v>136394</v>
+        <v>190755</v>
       </c>
       <c r="C20">
-        <v>110856</v>
+        <v>141942</v>
       </c>
       <c r="D20">
-        <v>123423</v>
+        <v>163972</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21">
-        <v>208646</v>
+        <v>263181</v>
       </c>
       <c r="C21">
-        <v>94208</v>
+        <v>135636</v>
       </c>
       <c r="D21">
-        <v>147432</v>
+        <v>194805</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22">
-        <v>68079</v>
+        <v>74241</v>
       </c>
       <c r="C22">
-        <v>33846</v>
+        <v>44581</v>
       </c>
       <c r="D22">
-        <v>42079</v>
+        <v>52551</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23">
-        <v>111971</v>
+        <v>198468</v>
       </c>
       <c r="C23">
-        <v>36682</v>
+        <v>88404</v>
       </c>
       <c r="D23">
-        <v>53725</v>
+        <v>113856</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24">
-        <v>169343</v>
+        <v>179472</v>
       </c>
       <c r="C24">
-        <v>130050</v>
+        <v>137260</v>
       </c>
       <c r="D24">
-        <v>137302</v>
+        <v>144026</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B25">
-        <v>95426</v>
+        <v>106815</v>
       </c>
       <c r="C25">
-        <v>58823</v>
+        <v>60702</v>
       </c>
       <c r="D25">
-        <v>70659</v>
+        <v>75524</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26">
-        <v>62311</v>
+        <v>80667</v>
       </c>
       <c r="C26">
-        <v>26413</v>
+        <v>40766</v>
       </c>
       <c r="D26">
-        <v>34070</v>
+        <v>50672</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27">
-        <v>29717</v>
+        <v>38157</v>
       </c>
       <c r="C27">
-        <v>16586</v>
+        <v>26014</v>
       </c>
       <c r="D27">
-        <v>20429</v>
+        <v>29157</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28">
-        <v>342107</v>
+        <v>380117</v>
       </c>
       <c r="C28">
-        <v>201643</v>
+        <v>250790</v>
       </c>
       <c r="D28">
-        <v>248610</v>
+        <v>299766</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B29">
-        <v>188931</v>
+        <v>197388</v>
       </c>
       <c r="C29">
-        <v>79441</v>
+        <v>88058</v>
       </c>
       <c r="D29">
-        <v>115172</v>
+        <v>122801</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B30">
-        <v>276568</v>
+        <v>382545</v>
       </c>
       <c r="C30">
-        <v>105979</v>
+        <v>141255</v>
       </c>
       <c r="D30">
-        <v>152942</v>
+        <v>218601</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31">
-        <v>178196</v>
+        <v>211529</v>
       </c>
       <c r="C31">
-        <v>94628</v>
+        <v>105280</v>
       </c>
       <c r="D31">
-        <v>121307</v>
+        <v>139047</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32">
-        <v>74537</v>
+        <v>99049</v>
       </c>
       <c r="C32">
-        <v>45941</v>
+        <v>59660</v>
       </c>
       <c r="D32">
-        <v>54690</v>
+        <v>71113</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B33">
-        <v>73375</v>
+        <v>149865</v>
       </c>
       <c r="C33">
-        <v>39198</v>
+        <v>70604</v>
       </c>
       <c r="D33">
-        <v>50061</v>
+        <v>96089</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B34">
-        <v>104383</v>
+        <v>161239</v>
       </c>
       <c r="C34">
-        <v>108547</v>
+        <v>155364</v>
       </c>
       <c r="D34">
-        <v>107060</v>
+        <v>157517</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35">
-        <v>25549</v>
+        <v>45108</v>
       </c>
       <c r="C35">
-        <v>14059</v>
+        <v>25844</v>
       </c>
       <c r="D35">
-        <v>15626</v>
+        <v>28440</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36">
-        <v>211550</v>
+        <v>182996</v>
       </c>
       <c r="C36">
-        <v>149456</v>
+        <v>201279</v>
       </c>
       <c r="D36">
-        <v>164922</v>
+        <v>195903</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B37">
-        <v>228225</v>
+        <v>292319</v>
       </c>
       <c r="C37">
-        <v>173362</v>
+        <v>211993</v>
       </c>
       <c r="D37">
-        <v>184996</v>
+        <v>233934</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B38">
-        <v>113759</v>
+        <v>155795</v>
       </c>
       <c r="C38">
-        <v>80276</v>
+        <v>110827</v>
       </c>
       <c r="D38">
-        <v>93083</v>
+        <v>127045</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39">
-        <v>65527</v>
+        <v>102862</v>
       </c>
       <c r="C39">
-        <v>43370</v>
+        <v>63737</v>
       </c>
       <c r="D39">
-        <v>51731</v>
+        <v>78231</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B40">
-        <v>149078</v>
+        <v>184527</v>
       </c>
       <c r="C40">
-        <v>78632</v>
+        <v>92577</v>
       </c>
       <c r="D40">
-        <v>101304</v>
+        <v>122906</v>
       </c>
     </row>
   </sheetData>
@@ -2006,6 +2007,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c78a888a-83d8-49bb-8890-6eb97e8a3c0e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100763DCA751E988E49B18D7A5F3E2E0A59" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5b021fe13dcae56d252e7321283a3f3b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd" xmlns:ns3="c78a888a-83d8-49bb-8890-6eb97e8a3c0e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d73ac3668dfd0d4084037886131f3a8" ns2:_="" ns3:_="">
     <xsd:import namespace="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
@@ -2248,41 +2269,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c78a888a-83d8-49bb-8890-6eb97e8a3c0e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1C2D98D-4316-42A5-A479-7A098215D7A8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B31F663-6144-4024-83F4-0C35A9D0D635}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
-    <ds:schemaRef ds:uri="c78a888a-83d8-49bb-8890-6eb97e8a3c0e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2305,9 +2295,26 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B31F663-6144-4024-83F4-0C35A9D0D635}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1C2D98D-4316-42A5-A479-7A098215D7A8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
+    <ds:schemaRef ds:uri="c78a888a-83d8-49bb-8890-6eb97e8a3c0e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{fd60f3b8-f236-4830-aecc-da0a7fc54679}" enabled="1" method="Standard" siteId="{76f33c20-5979-4408-adf7-8b3c4be95e52}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data/ansp_employment.xlsx
+++ b/data/ansp_employment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrauniom\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05718844-0B24-4333-B3E0-E93239EBEC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB8FDF7-4E73-433C-A42A-310EC738D5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="346" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="346" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="6" r:id="rId1"/>
@@ -1398,10 +1398,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>149000</v>
+        <v>184543</v>
       </c>
       <c r="C2">
-        <v>174600</v>
+        <v>214547</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1409,10 +1409,10 @@
         <v>41</v>
       </c>
       <c r="B3">
-        <v>78600</v>
+        <v>92569</v>
       </c>
       <c r="C3">
-        <v>96700</v>
+        <v>110728</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1420,10 +1420,10 @@
         <v>42</v>
       </c>
       <c r="B4">
-        <v>101300</v>
+        <v>122906</v>
       </c>
       <c r="C4">
-        <v>122900</v>
+        <v>146265</v>
       </c>
     </row>
   </sheetData>
@@ -1459,13 +1459,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>25157</v>
+        <v>48642</v>
       </c>
       <c r="C2">
-        <v>12004</v>
+        <v>21554</v>
       </c>
       <c r="D2">
-        <v>14278</v>
+        <v>27790</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1473,13 +1473,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>92480</v>
+        <v>198469</v>
       </c>
       <c r="C3">
-        <v>48890</v>
+        <v>79205</v>
       </c>
       <c r="D3">
-        <v>59632</v>
+        <v>107778</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1487,13 +1487,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>26608</v>
+        <v>51792</v>
       </c>
       <c r="C4">
-        <v>15573</v>
+        <v>34312</v>
       </c>
       <c r="D4">
-        <v>18564</v>
+        <v>38596</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1501,13 +1501,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>212241</v>
+        <v>267686</v>
       </c>
       <c r="C5">
-        <v>144827</v>
+        <v>182341</v>
       </c>
       <c r="D5">
-        <v>168198</v>
+        <v>213742</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1515,13 +1515,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>200980</v>
+        <v>187199</v>
       </c>
       <c r="C6">
-        <v>100844</v>
+        <v>116520</v>
       </c>
       <c r="D6">
-        <v>141867</v>
+        <v>152889</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1529,13 +1529,13 @@
         <v>46</v>
       </c>
       <c r="B7">
-        <v>33229</v>
+        <v>64772</v>
       </c>
       <c r="C7">
-        <v>27790</v>
+        <v>42073</v>
       </c>
       <c r="D7">
-        <v>29339</v>
+        <v>48367</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1543,13 +1543,13 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>97975</v>
+        <v>155130</v>
       </c>
       <c r="C8">
-        <v>43886</v>
+        <v>62556</v>
       </c>
       <c r="D8">
-        <v>57983</v>
+        <v>87175</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1557,13 +1557,13 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>114253</v>
+        <v>145458</v>
       </c>
       <c r="C9">
-        <v>55490</v>
+        <v>74829</v>
       </c>
       <c r="D9">
-        <v>75575</v>
+        <v>100709</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1571,13 +1571,13 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>103333</v>
+        <v>108233</v>
       </c>
       <c r="C10">
-        <v>65184</v>
+        <v>73413</v>
       </c>
       <c r="D10">
-        <v>82867</v>
+        <v>91027</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1585,13 +1585,13 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>259922</v>
+        <v>316618</v>
       </c>
       <c r="C11">
-        <v>108590</v>
+        <v>113654</v>
       </c>
       <c r="D11">
-        <v>154303</v>
+        <v>175360</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1599,13 +1599,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>48531</v>
+        <v>71841</v>
       </c>
       <c r="C12">
-        <v>13627</v>
+        <v>21157</v>
       </c>
       <c r="D12">
-        <v>21911</v>
+        <v>33835</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1613,13 +1613,13 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>135757</v>
+        <v>167984</v>
       </c>
       <c r="C13">
-        <v>101783</v>
+        <v>98285</v>
       </c>
       <c r="D13">
-        <v>114204</v>
+        <v>124721</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1627,13 +1627,13 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>118386</v>
+        <v>110742</v>
       </c>
       <c r="C14">
-        <v>44161</v>
+        <v>56439</v>
       </c>
       <c r="D14">
-        <v>68337</v>
+        <v>74638</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1641,13 +1641,13 @@
         <v>32</v>
       </c>
       <c r="B15">
-        <v>189385</v>
+        <v>214273</v>
       </c>
       <c r="C15">
-        <v>100512</v>
+        <v>119115</v>
       </c>
       <c r="D15">
-        <v>136938</v>
+        <v>157657</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1655,13 +1655,13 @@
         <v>13</v>
       </c>
       <c r="B16">
-        <v>160131</v>
+        <v>193267</v>
       </c>
       <c r="C16">
-        <v>107708</v>
+        <v>107704</v>
       </c>
       <c r="D16">
-        <v>131787</v>
+        <v>146573</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1669,13 +1669,13 @@
         <v>36</v>
       </c>
       <c r="B17">
-        <v>121324</v>
+        <v>122981</v>
       </c>
       <c r="C17">
-        <v>91881</v>
+        <v>83572</v>
       </c>
       <c r="D17">
-        <v>106711</v>
+        <v>102569</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1683,13 +1683,13 @@
         <v>47</v>
       </c>
       <c r="B18">
-        <v>79373</v>
+        <v>129617</v>
       </c>
       <c r="C18">
-        <v>56721</v>
+        <v>81951</v>
       </c>
       <c r="D18">
-        <v>64127</v>
+        <v>98098</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1697,13 +1697,13 @@
         <v>14</v>
       </c>
       <c r="B19">
-        <v>117751</v>
+        <v>143952</v>
       </c>
       <c r="C19">
-        <v>45005</v>
+        <v>65125</v>
       </c>
       <c r="D19">
-        <v>62468</v>
+        <v>85097</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1711,13 +1711,13 @@
         <v>15</v>
       </c>
       <c r="B20">
-        <v>136394</v>
+        <v>190775</v>
       </c>
       <c r="C20">
-        <v>110856</v>
+        <v>141942</v>
       </c>
       <c r="D20">
-        <v>123423</v>
+        <v>163972</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1725,13 +1725,13 @@
         <v>16</v>
       </c>
       <c r="B21">
-        <v>208646</v>
+        <v>263181</v>
       </c>
       <c r="C21">
-        <v>94208</v>
+        <v>135636</v>
       </c>
       <c r="D21">
-        <v>147432</v>
+        <v>194805</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1739,13 +1739,13 @@
         <v>17</v>
       </c>
       <c r="B22">
-        <v>68079</v>
+        <v>74241</v>
       </c>
       <c r="C22">
-        <v>33846</v>
+        <v>44581</v>
       </c>
       <c r="D22">
-        <v>42079</v>
+        <v>52551</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1753,13 +1753,13 @@
         <v>18</v>
       </c>
       <c r="B23">
-        <v>111971</v>
+        <v>198468</v>
       </c>
       <c r="C23">
-        <v>36682</v>
+        <v>88404</v>
       </c>
       <c r="D23">
-        <v>53725</v>
+        <v>113856</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1767,13 +1767,13 @@
         <v>19</v>
       </c>
       <c r="B24">
-        <v>169343</v>
+        <v>179472</v>
       </c>
       <c r="C24">
-        <v>130050</v>
+        <v>137260</v>
       </c>
       <c r="D24">
-        <v>137302</v>
+        <v>144026</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1781,13 +1781,13 @@
         <v>20</v>
       </c>
       <c r="B25">
-        <v>95426</v>
+        <v>106815</v>
       </c>
       <c r="C25">
-        <v>58823</v>
+        <v>60702</v>
       </c>
       <c r="D25">
-        <v>70659</v>
+        <v>75524</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1795,13 +1795,13 @@
         <v>21</v>
       </c>
       <c r="B26">
-        <v>62311</v>
+        <v>80667</v>
       </c>
       <c r="C26">
-        <v>26413</v>
+        <v>40766</v>
       </c>
       <c r="D26">
-        <v>34070</v>
+        <v>50672</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1809,13 +1809,13 @@
         <v>34</v>
       </c>
       <c r="B27">
-        <v>29717</v>
+        <v>38197</v>
       </c>
       <c r="C27">
-        <v>16586</v>
+        <v>26014</v>
       </c>
       <c r="D27">
-        <v>20429</v>
+        <v>29157</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1823,13 +1823,13 @@
         <v>22</v>
       </c>
       <c r="B28">
-        <v>342107</v>
+        <v>380117</v>
       </c>
       <c r="C28">
-        <v>201643</v>
+        <v>250790</v>
       </c>
       <c r="D28">
-        <v>248610</v>
+        <v>299760</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1837,13 +1837,13 @@
         <v>23</v>
       </c>
       <c r="B29">
-        <v>188931</v>
+        <v>197338</v>
       </c>
       <c r="C29">
-        <v>79441</v>
+        <v>88058</v>
       </c>
       <c r="D29">
-        <v>115172</v>
+        <v>122801</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1851,13 +1851,13 @@
         <v>24</v>
       </c>
       <c r="B30">
-        <v>276568</v>
+        <v>382545</v>
       </c>
       <c r="C30">
-        <v>105979</v>
+        <v>141255</v>
       </c>
       <c r="D30">
-        <v>152942</v>
+        <v>218601</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1865,13 +1865,13 @@
         <v>25</v>
       </c>
       <c r="B31">
-        <v>178196</v>
+        <v>211529</v>
       </c>
       <c r="C31">
-        <v>94628</v>
+        <v>105280</v>
       </c>
       <c r="D31">
-        <v>121307</v>
+        <v>139047</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1879,13 +1879,13 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>74537</v>
+        <v>99049</v>
       </c>
       <c r="C32">
-        <v>45941</v>
+        <v>59660</v>
       </c>
       <c r="D32">
-        <v>54690</v>
+        <v>71113</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1893,13 +1893,13 @@
         <v>26</v>
       </c>
       <c r="B33">
-        <v>73375</v>
+        <v>149865</v>
       </c>
       <c r="C33">
-        <v>39198</v>
+        <v>70604</v>
       </c>
       <c r="D33">
-        <v>50061</v>
+        <v>96089</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1907,13 +1907,13 @@
         <v>27</v>
       </c>
       <c r="B34">
-        <v>104383</v>
+        <v>161239</v>
       </c>
       <c r="C34">
-        <v>108547</v>
+        <v>155364</v>
       </c>
       <c r="D34">
-        <v>107060</v>
+        <v>157517</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1921,13 +1921,13 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>25549</v>
+        <v>45108</v>
       </c>
       <c r="C35">
-        <v>14059</v>
+        <v>25844</v>
       </c>
       <c r="D35">
-        <v>15626</v>
+        <v>28440</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1935,13 +1935,13 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>211550</v>
+        <v>182996</v>
       </c>
       <c r="C36">
-        <v>149456</v>
+        <v>201279</v>
       </c>
       <c r="D36">
-        <v>164922</v>
+        <v>195903</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1949,13 +1949,13 @@
         <v>28</v>
       </c>
       <c r="B37">
-        <v>228225</v>
+        <v>292319</v>
       </c>
       <c r="C37">
-        <v>173362</v>
+        <v>211993</v>
       </c>
       <c r="D37">
-        <v>184996</v>
+        <v>233934</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1963,13 +1963,13 @@
         <v>29</v>
       </c>
       <c r="B38">
-        <v>113759</v>
+        <v>155795</v>
       </c>
       <c r="C38">
-        <v>80276</v>
+        <v>110827</v>
       </c>
       <c r="D38">
-        <v>93083</v>
+        <v>127045</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1977,13 +1977,13 @@
         <v>30</v>
       </c>
       <c r="B39">
-        <v>65527</v>
+        <v>102862</v>
       </c>
       <c r="C39">
-        <v>43370</v>
+        <v>63737</v>
       </c>
       <c r="D39">
-        <v>51731</v>
+        <v>78321</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1991,13 +1991,13 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>149078</v>
+        <v>184543</v>
       </c>
       <c r="C40">
-        <v>78632</v>
+        <v>92569</v>
       </c>
       <c r="D40">
-        <v>101304</v>
+        <v>122906</v>
       </c>
     </row>
   </sheetData>
@@ -2006,6 +2006,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c78a888a-83d8-49bb-8890-6eb97e8a3c0e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100763DCA751E988E49B18D7A5F3E2E0A59" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5b021fe13dcae56d252e7321283a3f3b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd" xmlns:ns3="c78a888a-83d8-49bb-8890-6eb97e8a3c0e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d73ac3668dfd0d4084037886131f3a8" ns2:_="" ns3:_="">
     <xsd:import namespace="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
@@ -2248,17 +2259,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c78a888a-83d8-49bb-8890-6eb97e8a3c0e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2269,6 +2269,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A3ADF35-F119-4BE6-85A8-2E5C6C3A1AE7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c78a888a-83d8-49bb-8890-6eb97e8a3c0e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1C2D98D-4316-42A5-A479-7A098215D7A8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2287,27 +2304,16 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A3ADF35-F119-4BE6-85A8-2E5C6C3A1AE7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c78a888a-83d8-49bb-8890-6eb97e8a3c0e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B31F663-6144-4024-83F4-0C35A9D0D635}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{fd60f3b8-f236-4830-aecc-da0a7fc54679}" enabled="1" method="Standard" siteId="{76f33c20-5979-4408-adf7-8b3c4be95e52}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data/ansp_employment.xlsx
+++ b/data/ansp_employment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F160A74-85EC-459D-97B0-14A7CAA349D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B3823D-421A-48E5-B6E2-C18716B4A833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="346" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="18240" tabRatio="346" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="6" r:id="rId1"/>
@@ -908,8 +908,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="162">
     <cellStyle name="20 % - Accent1" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1398,10 +1399,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>184500</v>
+        <v>197600</v>
       </c>
       <c r="C2">
-        <v>214200</v>
+        <v>214000</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1409,10 +1410,10 @@
         <v>40</v>
       </c>
       <c r="B3">
-        <v>92600</v>
+        <v>95600</v>
       </c>
       <c r="C3">
-        <v>111000</v>
+        <v>102700</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1420,10 +1421,10 @@
         <v>41</v>
       </c>
       <c r="B4">
-        <v>122900</v>
+        <v>128800</v>
       </c>
       <c r="C4">
-        <v>146500</v>
+        <v>136700</v>
       </c>
     </row>
   </sheetData>
@@ -1457,548 +1458,548 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>48642</v>
-      </c>
-      <c r="C2">
-        <v>21554</v>
-      </c>
-      <c r="D2">
-        <v>27790</v>
+        <v>48</v>
+      </c>
+      <c r="B2" s="1">
+        <v>197947.36842105264</v>
+      </c>
+      <c r="C2" s="1">
+        <v>135901.63934426228</v>
+      </c>
+      <c r="D2" s="1">
+        <v>163664.85507246378</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>198469</v>
-      </c>
-      <c r="C3">
-        <v>79205</v>
-      </c>
-      <c r="D3">
-        <v>107778</v>
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>79101.694915254237</v>
+      </c>
+      <c r="C3" s="1">
+        <v>24512.635379061372</v>
+      </c>
+      <c r="D3" s="1">
+        <v>34098.214285714283</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>51792</v>
-      </c>
-      <c r="C4">
-        <v>34312</v>
-      </c>
-      <c r="D4">
-        <v>38956</v>
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <v>225026.66666666666</v>
+      </c>
+      <c r="C4" s="1">
+        <v>86047.489823609227</v>
+      </c>
+      <c r="D4" s="1">
+        <v>118553.01455301455</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>267686</v>
-      </c>
-      <c r="C5">
-        <v>182341</v>
-      </c>
-      <c r="D5">
-        <v>213742</v>
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <v>58229.729729729726</v>
+      </c>
+      <c r="C5" s="1">
+        <v>34284.313725490196</v>
+      </c>
+      <c r="D5" s="1">
+        <v>40658.273381294959</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>187199</v>
-      </c>
-      <c r="C6">
-        <v>116520</v>
-      </c>
-      <c r="D6">
-        <v>152889</v>
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
+        <v>299335.46325878589</v>
+      </c>
+      <c r="C6" s="1">
+        <v>178264.55026455026</v>
+      </c>
+      <c r="D6" s="1">
+        <v>221327.27272727271</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7">
-        <v>64772</v>
-      </c>
-      <c r="C7">
-        <v>42073</v>
-      </c>
-      <c r="D7">
-        <v>48367</v>
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>181687.16577540108</v>
+      </c>
+      <c r="C7" s="1">
+        <v>115543.28358208956</v>
+      </c>
+      <c r="D7" s="1">
+        <v>150434.41466854725</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>155130</v>
-      </c>
-      <c r="C8">
-        <v>62556</v>
-      </c>
-      <c r="D8">
-        <v>87175</v>
+        <v>45</v>
+      </c>
+      <c r="B8" s="1">
+        <v>75750</v>
+      </c>
+      <c r="C8" s="1">
+        <v>42439.393939393936</v>
+      </c>
+      <c r="D8" s="1">
+        <v>51537.444933920706</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>145458</v>
-      </c>
-      <c r="C9">
-        <v>74829</v>
-      </c>
-      <c r="D9">
-        <v>100709</v>
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>163924.65753424657</v>
+      </c>
+      <c r="C9" s="1">
+        <v>64971.428571428572</v>
+      </c>
+      <c r="D9" s="1">
+        <v>90496.46643109541</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>108233</v>
-      </c>
-      <c r="C10">
-        <v>73413</v>
-      </c>
-      <c r="D10">
-        <v>91027</v>
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>158888.03088803089</v>
+      </c>
+      <c r="C10" s="1">
+        <v>74991.228070175435</v>
+      </c>
+      <c r="D10" s="1">
+        <v>105381.81818181818</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>316618</v>
-      </c>
-      <c r="C11">
-        <v>113654</v>
-      </c>
-      <c r="D11">
-        <v>175360</v>
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>114778.62595419848</v>
+      </c>
+      <c r="C11" s="1">
+        <v>80591.666666666672</v>
+      </c>
+      <c r="D11" s="1">
+        <v>98434.262948207179</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>71841</v>
-      </c>
-      <c r="C12">
-        <v>21157</v>
-      </c>
-      <c r="D12">
-        <v>33835</v>
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>312645.03816793894</v>
+      </c>
+      <c r="C12" s="1">
+        <v>120788.66124052764</v>
+      </c>
+      <c r="D12" s="1">
+        <v>179522.49269717623</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>167984</v>
-      </c>
-      <c r="C13">
-        <v>98285</v>
-      </c>
-      <c r="D13">
-        <v>124721</v>
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>86623.136246786627</v>
+      </c>
+      <c r="C13" s="1">
+        <v>25453.386024788935</v>
+      </c>
+      <c r="D13" s="1">
+        <v>41291.400425985092</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>110742</v>
-      </c>
-      <c r="C14">
-        <v>56439</v>
-      </c>
-      <c r="D14">
-        <v>74638</v>
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>180443.58794674141</v>
+      </c>
+      <c r="C14" s="1">
+        <v>96235.753960090515</v>
+      </c>
+      <c r="D14" s="1">
+        <v>127386.64938431628</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15">
-        <v>214273</v>
-      </c>
-      <c r="C15">
-        <v>119115</v>
-      </c>
-      <c r="D15">
-        <v>157657</v>
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>128122.80701754386</v>
+      </c>
+      <c r="C15" s="1">
+        <v>59276.119402985074</v>
+      </c>
+      <c r="D15" s="1">
+        <v>79821.989528795806</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16">
-        <v>193267</v>
-      </c>
-      <c r="C16">
-        <v>107704</v>
-      </c>
-      <c r="D16">
-        <v>146573</v>
+        <v>31</v>
+      </c>
+      <c r="B16" s="1">
+        <v>236884.54600120263</v>
+      </c>
+      <c r="C16" s="1">
+        <v>112655.61843168958</v>
+      </c>
+      <c r="D16" s="1">
+        <v>162593.42518733381</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17">
-        <v>122981</v>
-      </c>
-      <c r="C17">
-        <v>83572</v>
-      </c>
-      <c r="D17">
-        <v>102569</v>
+        <v>13</v>
+      </c>
+      <c r="B17" s="1">
+        <v>201653.56083086052</v>
+      </c>
+      <c r="C17" s="1">
+        <v>108748.61367837338</v>
+      </c>
+      <c r="D17" s="1">
+        <v>150901.38000673172</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18">
-        <v>129617</v>
-      </c>
-      <c r="C18">
-        <v>81951</v>
-      </c>
-      <c r="D18">
-        <v>98098</v>
+        <v>35</v>
+      </c>
+      <c r="B18" s="1">
+        <v>128750</v>
+      </c>
+      <c r="C18" s="1">
+        <v>89880.681818181809</v>
+      </c>
+      <c r="D18" s="1">
+        <v>108389.88095238095</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19">
-        <v>143952</v>
-      </c>
-      <c r="C19">
-        <v>65125</v>
-      </c>
-      <c r="D19">
-        <v>85097</v>
+        <v>46</v>
+      </c>
+      <c r="B19" s="1">
+        <v>136454.72061657035</v>
+      </c>
+      <c r="C19" s="1">
+        <v>85303.571428571435</v>
+      </c>
+      <c r="D19" s="1">
+        <v>102688.93254747872</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20">
-        <v>190755</v>
-      </c>
-      <c r="C20">
-        <v>141942</v>
-      </c>
-      <c r="D20">
-        <v>163972</v>
+        <v>14</v>
+      </c>
+      <c r="B20" s="1">
+        <v>195768.42105263157</v>
+      </c>
+      <c r="C20" s="1">
+        <v>75214.650766609877</v>
+      </c>
+      <c r="D20" s="1">
+        <v>104693.69369369368</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
-      <c r="B21">
-        <v>263181</v>
-      </c>
-      <c r="C21">
-        <v>135636</v>
-      </c>
-      <c r="D21">
-        <v>194805</v>
+      <c r="B21" s="1">
+        <v>221116.58031088085</v>
+      </c>
+      <c r="C21" s="1">
+        <v>148255.86353944565</v>
+      </c>
+      <c r="D21" s="1">
+        <v>181149.70760233919</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
-      <c r="B22">
-        <v>74241</v>
-      </c>
-      <c r="C22">
-        <v>44581</v>
-      </c>
-      <c r="D22">
-        <v>52551</v>
+      <c r="B22" s="1">
+        <v>84849.315068493161</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46611.353711790391</v>
+      </c>
+      <c r="D22" s="1">
+        <v>55854.304635761589</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>17</v>
       </c>
-      <c r="B23">
-        <v>198468</v>
-      </c>
-      <c r="C23">
-        <v>88404</v>
-      </c>
-      <c r="D23">
-        <v>113856</v>
+      <c r="B23" s="1">
+        <v>200441.66666666666</v>
+      </c>
+      <c r="C23" s="1">
+        <v>86278.215223097111</v>
+      </c>
+      <c r="D23" s="1">
+        <v>113622.75449101796</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>18</v>
       </c>
-      <c r="B24">
-        <v>179472</v>
-      </c>
-      <c r="C24">
-        <v>137260</v>
-      </c>
-      <c r="D24">
-        <v>144026</v>
+      <c r="B24" s="1">
+        <v>199467.00507614212</v>
+      </c>
+      <c r="C24" s="1">
+        <v>147289.56834532376</v>
+      </c>
+      <c r="D24" s="1">
+        <v>155142.09320091672</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>19</v>
       </c>
-      <c r="B25">
-        <v>106815</v>
-      </c>
-      <c r="C25">
-        <v>60702</v>
-      </c>
-      <c r="D25">
-        <v>75524</v>
+      <c r="B25" s="1">
+        <v>125833.33333333333</v>
+      </c>
+      <c r="C25" s="1">
+        <v>69125</v>
+      </c>
+      <c r="D25" s="1">
+        <v>86724.137931034478</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>20</v>
       </c>
-      <c r="B26">
-        <v>80667</v>
-      </c>
-      <c r="C26">
-        <v>40766</v>
-      </c>
-      <c r="D26">
-        <v>50672</v>
+      <c r="B26" s="1">
+        <v>93081.08108108108</v>
+      </c>
+      <c r="C26" s="1">
+        <v>45140.186915887854</v>
+      </c>
+      <c r="D26" s="1">
+        <v>57458.333333333336</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>33</v>
       </c>
-      <c r="B27">
-        <v>38157</v>
-      </c>
-      <c r="C27">
-        <v>26014</v>
-      </c>
-      <c r="D27">
-        <v>29157</v>
+      <c r="B27" s="1">
+        <v>45345.454545454544</v>
+      </c>
+      <c r="C27" s="1">
+        <v>34909.090909090904</v>
+      </c>
+      <c r="D27" s="1">
+        <v>37808.080808080813</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>21</v>
       </c>
-      <c r="B28">
-        <v>380117</v>
-      </c>
-      <c r="C28">
-        <v>250790</v>
-      </c>
-      <c r="D28">
-        <v>299766</v>
+      <c r="B28" s="1">
+        <v>420830.7086614173</v>
+      </c>
+      <c r="C28" s="1">
+        <v>276735.49883990717</v>
+      </c>
+      <c r="D28" s="1">
+        <v>330166.42335766426</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
-      <c r="B29">
-        <v>197388</v>
-      </c>
-      <c r="C29">
-        <v>88058</v>
-      </c>
-      <c r="D29">
-        <v>122801</v>
+      <c r="B29" s="1">
+        <v>224110.47928513403</v>
+      </c>
+      <c r="C29" s="1">
+        <v>91534.086895090077</v>
+      </c>
+      <c r="D29" s="1">
+        <v>131711.71836533726</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>23</v>
       </c>
-      <c r="B30">
-        <v>382545</v>
-      </c>
-      <c r="C30">
-        <v>141255</v>
-      </c>
-      <c r="D30">
-        <v>218601</v>
+      <c r="B30" s="1">
+        <v>378004.80769230769</v>
+      </c>
+      <c r="C30" s="1">
+        <v>155812.06496519721</v>
+      </c>
+      <c r="D30" s="1">
+        <v>228137.71517996868</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>24</v>
       </c>
-      <c r="B31">
-        <v>211529</v>
-      </c>
-      <c r="C31">
-        <v>105280</v>
-      </c>
-      <c r="D31">
-        <v>139047</v>
+      <c r="B31" s="1">
+        <v>223375.63451776648</v>
+      </c>
+      <c r="C31" s="1">
+        <v>114296.03729603729</v>
+      </c>
+      <c r="D31" s="1">
+        <v>148623.00319488818</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>30</v>
       </c>
-      <c r="B32">
-        <v>99049</v>
-      </c>
-      <c r="C32">
-        <v>59660</v>
-      </c>
-      <c r="D32">
-        <v>71113</v>
+      <c r="B32" s="1">
+        <v>97144.578313253005</v>
+      </c>
+      <c r="C32" s="1">
+        <v>63301.980198019803</v>
+      </c>
+      <c r="D32" s="1">
+        <v>73157.894736842107</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>25</v>
       </c>
-      <c r="B33">
-        <v>149865</v>
-      </c>
-      <c r="C33">
-        <v>70604</v>
-      </c>
-      <c r="D33">
-        <v>96089</v>
+      <c r="B33" s="1">
+        <v>191636.52173913043</v>
+      </c>
+      <c r="C33" s="1">
+        <v>70301.043219076004</v>
+      </c>
+      <c r="D33" s="1">
+        <v>106695.35732916015</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>26</v>
       </c>
-      <c r="B34">
-        <v>161239</v>
-      </c>
-      <c r="C34">
-        <v>155364</v>
-      </c>
-      <c r="D34">
-        <v>157517</v>
+      <c r="B34" s="1">
+        <v>187862.63736263738</v>
+      </c>
+      <c r="C34" s="1">
+        <v>150753.02419354839</v>
+      </c>
+      <c r="D34" s="1">
+        <v>163927.17815344603</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>32</v>
       </c>
-      <c r="B35">
-        <v>45108</v>
-      </c>
-      <c r="C35">
-        <v>25844</v>
-      </c>
-      <c r="D35">
-        <v>28440</v>
+      <c r="B35" s="1">
+        <v>48451.327433628321</v>
+      </c>
+      <c r="C35" s="1">
+        <v>31896.755162241887</v>
+      </c>
+      <c r="D35" s="1">
+        <v>34261.694058154237</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>34</v>
       </c>
-      <c r="B36">
-        <v>182996</v>
-      </c>
-      <c r="C36">
-        <v>201279</v>
-      </c>
-      <c r="D36">
-        <v>195903</v>
+      <c r="B36" s="1">
+        <v>243027.55905511809</v>
+      </c>
+      <c r="C36" s="1">
+        <v>181887.12522045855</v>
+      </c>
+      <c r="D36" s="1">
+        <v>200802.67965895249</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
-      <c r="B37">
-        <v>292319</v>
-      </c>
-      <c r="C37">
-        <v>211993</v>
-      </c>
-      <c r="D37">
-        <v>233934</v>
+      <c r="B37" s="1">
+        <v>281726.49572649575</v>
+      </c>
+      <c r="C37" s="1">
+        <v>238065.0406504065</v>
+      </c>
+      <c r="D37" s="1">
+        <v>249544.56928838952</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>28</v>
       </c>
-      <c r="B38">
-        <v>155795</v>
-      </c>
-      <c r="C38">
-        <v>110827</v>
-      </c>
-      <c r="D38">
-        <v>127045</v>
+      <c r="B38" s="1">
+        <v>173172.41379310345</v>
+      </c>
+      <c r="C38" s="1">
+        <v>104307.69230769231</v>
+      </c>
+      <c r="D38" s="1">
+        <v>127710.9375</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>29</v>
       </c>
-      <c r="B39">
-        <v>102862</v>
-      </c>
-      <c r="C39">
-        <v>63737</v>
-      </c>
-      <c r="D39">
-        <v>78231</v>
+      <c r="B39" s="1">
+        <v>114057.69230769231</v>
+      </c>
+      <c r="C39" s="1">
+        <v>69183.673469387752</v>
+      </c>
+      <c r="D39" s="1">
+        <v>85635.722679200931</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>47</v>
       </c>
-      <c r="B40">
-        <v>184527</v>
-      </c>
-      <c r="C40">
-        <v>92577</v>
-      </c>
-      <c r="D40">
-        <v>122906</v>
+      <c r="B40" s="1">
+        <v>197670.85798816569</v>
+      </c>
+      <c r="C40" s="1">
+        <v>95667.33466933867</v>
+      </c>
+      <c r="D40" s="1">
+        <v>128865.74819917411</v>
       </c>
     </row>
   </sheetData>
@@ -2007,15 +2008,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd">
@@ -2026,7 +2018,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100763DCA751E988E49B18D7A5F3E2E0A59" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5b021fe13dcae56d252e7321283a3f3b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd" xmlns:ns3="c78a888a-83d8-49bb-8890-6eb97e8a3c0e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d73ac3668dfd0d4084037886131f3a8" ns2:_="" ns3:_="">
     <xsd:import namespace="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
@@ -2269,15 +2261,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B31F663-6144-4024-83F4-0C35A9D0D635}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A3ADF35-F119-4BE6-85A8-2E5C6C3A1AE7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -2294,7 +2287,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1C2D98D-4316-42A5-A479-7A098215D7A8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2313,6 +2306,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B31F663-6144-4024-83F4-0C35A9D0D635}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{fd60f3b8-f236-4830-aecc-da0a7fc54679}" enabled="1" method="Standard" siteId="{76f33c20-5979-4408-adf7-8b3c4be95e52}" contentBits="0" removed="0"/>

--- a/data/ansp_employment.xlsx
+++ b/data/ansp_employment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05718844-0B24-4333-B3E0-E93239EBEC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B3823D-421A-48E5-B6E2-C18716B4A833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="346" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="18240" tabRatio="346" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="6" r:id="rId1"/>
@@ -81,9 +81,6 @@
     <t>HungaroControl</t>
   </si>
   <si>
-    <t>IAA</t>
-  </si>
-  <si>
     <t>LFV</t>
   </si>
   <si>
@@ -181,6 +178,9 @@
   </si>
   <si>
     <t>EUROCONTROL area - average values</t>
+  </si>
+  <si>
+    <t>AirNav Ireland</t>
   </si>
 </sst>
 </file>
@@ -908,8 +908,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="162">
     <cellStyle name="20 % - Accent1" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1384,13 +1385,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1398,32 +1399,32 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>149000</v>
+        <v>197600</v>
       </c>
       <c r="C2">
-        <v>174600</v>
+        <v>214000</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3">
-        <v>78600</v>
+        <v>95600</v>
       </c>
       <c r="C3">
-        <v>96700</v>
+        <v>102700</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4">
-        <v>101300</v>
+        <v>128800</v>
       </c>
       <c r="C4">
-        <v>122900</v>
+        <v>136700</v>
       </c>
     </row>
   </sheetData>
@@ -1438,566 +1439,567 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>38</v>
-      </c>
-      <c r="D1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>25157</v>
-      </c>
-      <c r="C2">
-        <v>12004</v>
-      </c>
-      <c r="D2">
-        <v>14278</v>
+        <v>48</v>
+      </c>
+      <c r="B2" s="1">
+        <v>197947.36842105264</v>
+      </c>
+      <c r="C2" s="1">
+        <v>135901.63934426228</v>
+      </c>
+      <c r="D2" s="1">
+        <v>163664.85507246378</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>92480</v>
-      </c>
-      <c r="C3">
-        <v>48890</v>
-      </c>
-      <c r="D3">
-        <v>59632</v>
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>79101.694915254237</v>
+      </c>
+      <c r="C3" s="1">
+        <v>24512.635379061372</v>
+      </c>
+      <c r="D3" s="1">
+        <v>34098.214285714283</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>26608</v>
-      </c>
-      <c r="C4">
-        <v>15573</v>
-      </c>
-      <c r="D4">
-        <v>18564</v>
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <v>225026.66666666666</v>
+      </c>
+      <c r="C4" s="1">
+        <v>86047.489823609227</v>
+      </c>
+      <c r="D4" s="1">
+        <v>118553.01455301455</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>212241</v>
-      </c>
-      <c r="C5">
-        <v>144827</v>
-      </c>
-      <c r="D5">
-        <v>168198</v>
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <v>58229.729729729726</v>
+      </c>
+      <c r="C5" s="1">
+        <v>34284.313725490196</v>
+      </c>
+      <c r="D5" s="1">
+        <v>40658.273381294959</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>200980</v>
-      </c>
-      <c r="C6">
-        <v>100844</v>
-      </c>
-      <c r="D6">
-        <v>141867</v>
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
+        <v>299335.46325878589</v>
+      </c>
+      <c r="C6" s="1">
+        <v>178264.55026455026</v>
+      </c>
+      <c r="D6" s="1">
+        <v>221327.27272727271</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7">
-        <v>33229</v>
-      </c>
-      <c r="C7">
-        <v>27790</v>
-      </c>
-      <c r="D7">
-        <v>29339</v>
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>181687.16577540108</v>
+      </c>
+      <c r="C7" s="1">
+        <v>115543.28358208956</v>
+      </c>
+      <c r="D7" s="1">
+        <v>150434.41466854725</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>97975</v>
-      </c>
-      <c r="C8">
-        <v>43886</v>
-      </c>
-      <c r="D8">
-        <v>57983</v>
+        <v>45</v>
+      </c>
+      <c r="B8" s="1">
+        <v>75750</v>
+      </c>
+      <c r="C8" s="1">
+        <v>42439.393939393936</v>
+      </c>
+      <c r="D8" s="1">
+        <v>51537.444933920706</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>114253</v>
-      </c>
-      <c r="C9">
-        <v>55490</v>
-      </c>
-      <c r="D9">
-        <v>75575</v>
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>163924.65753424657</v>
+      </c>
+      <c r="C9" s="1">
+        <v>64971.428571428572</v>
+      </c>
+      <c r="D9" s="1">
+        <v>90496.46643109541</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>103333</v>
-      </c>
-      <c r="C10">
-        <v>65184</v>
-      </c>
-      <c r="D10">
-        <v>82867</v>
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>158888.03088803089</v>
+      </c>
+      <c r="C10" s="1">
+        <v>74991.228070175435</v>
+      </c>
+      <c r="D10" s="1">
+        <v>105381.81818181818</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>259922</v>
-      </c>
-      <c r="C11">
-        <v>108590</v>
-      </c>
-      <c r="D11">
-        <v>154303</v>
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>114778.62595419848</v>
+      </c>
+      <c r="C11" s="1">
+        <v>80591.666666666672</v>
+      </c>
+      <c r="D11" s="1">
+        <v>98434.262948207179</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>48531</v>
-      </c>
-      <c r="C12">
-        <v>13627</v>
-      </c>
-      <c r="D12">
-        <v>21911</v>
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>312645.03816793894</v>
+      </c>
+      <c r="C12" s="1">
+        <v>120788.66124052764</v>
+      </c>
+      <c r="D12" s="1">
+        <v>179522.49269717623</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>135757</v>
-      </c>
-      <c r="C13">
-        <v>101783</v>
-      </c>
-      <c r="D13">
-        <v>114204</v>
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>86623.136246786627</v>
+      </c>
+      <c r="C13" s="1">
+        <v>25453.386024788935</v>
+      </c>
+      <c r="D13" s="1">
+        <v>41291.400425985092</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>118386</v>
-      </c>
-      <c r="C14">
-        <v>44161</v>
-      </c>
-      <c r="D14">
-        <v>68337</v>
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>180443.58794674141</v>
+      </c>
+      <c r="C14" s="1">
+        <v>96235.753960090515</v>
+      </c>
+      <c r="D14" s="1">
+        <v>127386.64938431628</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15">
-        <v>189385</v>
-      </c>
-      <c r="C15">
-        <v>100512</v>
-      </c>
-      <c r="D15">
-        <v>136938</v>
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>128122.80701754386</v>
+      </c>
+      <c r="C15" s="1">
+        <v>59276.119402985074</v>
+      </c>
+      <c r="D15" s="1">
+        <v>79821.989528795806</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16">
-        <v>160131</v>
-      </c>
-      <c r="C16">
-        <v>107708</v>
-      </c>
-      <c r="D16">
-        <v>131787</v>
+        <v>31</v>
+      </c>
+      <c r="B16" s="1">
+        <v>236884.54600120263</v>
+      </c>
+      <c r="C16" s="1">
+        <v>112655.61843168958</v>
+      </c>
+      <c r="D16" s="1">
+        <v>162593.42518733381</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17">
-        <v>121324</v>
-      </c>
-      <c r="C17">
-        <v>91881</v>
-      </c>
-      <c r="D17">
-        <v>106711</v>
+        <v>13</v>
+      </c>
+      <c r="B17" s="1">
+        <v>201653.56083086052</v>
+      </c>
+      <c r="C17" s="1">
+        <v>108748.61367837338</v>
+      </c>
+      <c r="D17" s="1">
+        <v>150901.38000673172</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18">
-        <v>79373</v>
-      </c>
-      <c r="C18">
-        <v>56721</v>
-      </c>
-      <c r="D18">
-        <v>64127</v>
+        <v>35</v>
+      </c>
+      <c r="B18" s="1">
+        <v>128750</v>
+      </c>
+      <c r="C18" s="1">
+        <v>89880.681818181809</v>
+      </c>
+      <c r="D18" s="1">
+        <v>108389.88095238095</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19">
-        <v>117751</v>
-      </c>
-      <c r="C19">
-        <v>45005</v>
-      </c>
-      <c r="D19">
-        <v>62468</v>
+        <v>46</v>
+      </c>
+      <c r="B19" s="1">
+        <v>136454.72061657035</v>
+      </c>
+      <c r="C19" s="1">
+        <v>85303.571428571435</v>
+      </c>
+      <c r="D19" s="1">
+        <v>102688.93254747872</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20">
-        <v>136394</v>
-      </c>
-      <c r="C20">
-        <v>110856</v>
-      </c>
-      <c r="D20">
-        <v>123423</v>
+        <v>14</v>
+      </c>
+      <c r="B20" s="1">
+        <v>195768.42105263157</v>
+      </c>
+      <c r="C20" s="1">
+        <v>75214.650766609877</v>
+      </c>
+      <c r="D20" s="1">
+        <v>104693.69369369368</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21">
-        <v>208646</v>
-      </c>
-      <c r="C21">
-        <v>94208</v>
-      </c>
-      <c r="D21">
-        <v>147432</v>
+        <v>15</v>
+      </c>
+      <c r="B21" s="1">
+        <v>221116.58031088085</v>
+      </c>
+      <c r="C21" s="1">
+        <v>148255.86353944565</v>
+      </c>
+      <c r="D21" s="1">
+        <v>181149.70760233919</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22">
-        <v>68079</v>
-      </c>
-      <c r="C22">
-        <v>33846</v>
-      </c>
-      <c r="D22">
-        <v>42079</v>
+        <v>16</v>
+      </c>
+      <c r="B22" s="1">
+        <v>84849.315068493161</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46611.353711790391</v>
+      </c>
+      <c r="D22" s="1">
+        <v>55854.304635761589</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23">
-        <v>111971</v>
-      </c>
-      <c r="C23">
-        <v>36682</v>
-      </c>
-      <c r="D23">
-        <v>53725</v>
+        <v>17</v>
+      </c>
+      <c r="B23" s="1">
+        <v>200441.66666666666</v>
+      </c>
+      <c r="C23" s="1">
+        <v>86278.215223097111</v>
+      </c>
+      <c r="D23" s="1">
+        <v>113622.75449101796</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24">
-        <v>169343</v>
-      </c>
-      <c r="C24">
-        <v>130050</v>
-      </c>
-      <c r="D24">
-        <v>137302</v>
+        <v>18</v>
+      </c>
+      <c r="B24" s="1">
+        <v>199467.00507614212</v>
+      </c>
+      <c r="C24" s="1">
+        <v>147289.56834532376</v>
+      </c>
+      <c r="D24" s="1">
+        <v>155142.09320091672</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25">
-        <v>95426</v>
-      </c>
-      <c r="C25">
-        <v>58823</v>
-      </c>
-      <c r="D25">
-        <v>70659</v>
+        <v>19</v>
+      </c>
+      <c r="B25" s="1">
+        <v>125833.33333333333</v>
+      </c>
+      <c r="C25" s="1">
+        <v>69125</v>
+      </c>
+      <c r="D25" s="1">
+        <v>86724.137931034478</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26">
-        <v>62311</v>
-      </c>
-      <c r="C26">
-        <v>26413</v>
-      </c>
-      <c r="D26">
-        <v>34070</v>
+        <v>20</v>
+      </c>
+      <c r="B26" s="1">
+        <v>93081.08108108108</v>
+      </c>
+      <c r="C26" s="1">
+        <v>45140.186915887854</v>
+      </c>
+      <c r="D26" s="1">
+        <v>57458.333333333336</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27">
-        <v>29717</v>
-      </c>
-      <c r="C27">
-        <v>16586</v>
-      </c>
-      <c r="D27">
-        <v>20429</v>
+        <v>33</v>
+      </c>
+      <c r="B27" s="1">
+        <v>45345.454545454544</v>
+      </c>
+      <c r="C27" s="1">
+        <v>34909.090909090904</v>
+      </c>
+      <c r="D27" s="1">
+        <v>37808.080808080813</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28">
-        <v>342107</v>
-      </c>
-      <c r="C28">
-        <v>201643</v>
-      </c>
-      <c r="D28">
-        <v>248610</v>
+        <v>21</v>
+      </c>
+      <c r="B28" s="1">
+        <v>420830.7086614173</v>
+      </c>
+      <c r="C28" s="1">
+        <v>276735.49883990717</v>
+      </c>
+      <c r="D28" s="1">
+        <v>330166.42335766426</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29">
-        <v>188931</v>
-      </c>
-      <c r="C29">
-        <v>79441</v>
-      </c>
-      <c r="D29">
-        <v>115172</v>
+        <v>22</v>
+      </c>
+      <c r="B29" s="1">
+        <v>224110.47928513403</v>
+      </c>
+      <c r="C29" s="1">
+        <v>91534.086895090077</v>
+      </c>
+      <c r="D29" s="1">
+        <v>131711.71836533726</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30">
-        <v>276568</v>
-      </c>
-      <c r="C30">
-        <v>105979</v>
-      </c>
-      <c r="D30">
-        <v>152942</v>
+        <v>23</v>
+      </c>
+      <c r="B30" s="1">
+        <v>378004.80769230769</v>
+      </c>
+      <c r="C30" s="1">
+        <v>155812.06496519721</v>
+      </c>
+      <c r="D30" s="1">
+        <v>228137.71517996868</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31">
-        <v>178196</v>
-      </c>
-      <c r="C31">
-        <v>94628</v>
-      </c>
-      <c r="D31">
-        <v>121307</v>
+        <v>24</v>
+      </c>
+      <c r="B31" s="1">
+        <v>223375.63451776648</v>
+      </c>
+      <c r="C31" s="1">
+        <v>114296.03729603729</v>
+      </c>
+      <c r="D31" s="1">
+        <v>148623.00319488818</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32">
-        <v>74537</v>
-      </c>
-      <c r="C32">
-        <v>45941</v>
-      </c>
-      <c r="D32">
-        <v>54690</v>
+        <v>30</v>
+      </c>
+      <c r="B32" s="1">
+        <v>97144.578313253005</v>
+      </c>
+      <c r="C32" s="1">
+        <v>63301.980198019803</v>
+      </c>
+      <c r="D32" s="1">
+        <v>73157.894736842107</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33">
-        <v>73375</v>
-      </c>
-      <c r="C33">
-        <v>39198</v>
-      </c>
-      <c r="D33">
-        <v>50061</v>
+        <v>25</v>
+      </c>
+      <c r="B33" s="1">
+        <v>191636.52173913043</v>
+      </c>
+      <c r="C33" s="1">
+        <v>70301.043219076004</v>
+      </c>
+      <c r="D33" s="1">
+        <v>106695.35732916015</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34">
-        <v>104383</v>
-      </c>
-      <c r="C34">
-        <v>108547</v>
-      </c>
-      <c r="D34">
-        <v>107060</v>
+        <v>26</v>
+      </c>
+      <c r="B34" s="1">
+        <v>187862.63736263738</v>
+      </c>
+      <c r="C34" s="1">
+        <v>150753.02419354839</v>
+      </c>
+      <c r="D34" s="1">
+        <v>163927.17815344603</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35">
-        <v>25549</v>
-      </c>
-      <c r="C35">
-        <v>14059</v>
-      </c>
-      <c r="D35">
-        <v>15626</v>
+        <v>32</v>
+      </c>
+      <c r="B35" s="1">
+        <v>48451.327433628321</v>
+      </c>
+      <c r="C35" s="1">
+        <v>31896.755162241887</v>
+      </c>
+      <c r="D35" s="1">
+        <v>34261.694058154237</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36">
-        <v>211550</v>
-      </c>
-      <c r="C36">
-        <v>149456</v>
-      </c>
-      <c r="D36">
-        <v>164922</v>
+        <v>34</v>
+      </c>
+      <c r="B36" s="1">
+        <v>243027.55905511809</v>
+      </c>
+      <c r="C36" s="1">
+        <v>181887.12522045855</v>
+      </c>
+      <c r="D36" s="1">
+        <v>200802.67965895249</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>28</v>
-      </c>
-      <c r="B37">
-        <v>228225</v>
-      </c>
-      <c r="C37">
-        <v>173362</v>
-      </c>
-      <c r="D37">
-        <v>184996</v>
+        <v>27</v>
+      </c>
+      <c r="B37" s="1">
+        <v>281726.49572649575</v>
+      </c>
+      <c r="C37" s="1">
+        <v>238065.0406504065</v>
+      </c>
+      <c r="D37" s="1">
+        <v>249544.56928838952</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>29</v>
-      </c>
-      <c r="B38">
-        <v>113759</v>
-      </c>
-      <c r="C38">
-        <v>80276</v>
-      </c>
-      <c r="D38">
-        <v>93083</v>
+        <v>28</v>
+      </c>
+      <c r="B38" s="1">
+        <v>173172.41379310345</v>
+      </c>
+      <c r="C38" s="1">
+        <v>104307.69230769231</v>
+      </c>
+      <c r="D38" s="1">
+        <v>127710.9375</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>30</v>
-      </c>
-      <c r="B39">
-        <v>65527</v>
-      </c>
-      <c r="C39">
-        <v>43370</v>
-      </c>
-      <c r="D39">
-        <v>51731</v>
+        <v>29</v>
+      </c>
+      <c r="B39" s="1">
+        <v>114057.69230769231</v>
+      </c>
+      <c r="C39" s="1">
+        <v>69183.673469387752</v>
+      </c>
+      <c r="D39" s="1">
+        <v>85635.722679200931</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40">
-        <v>149078</v>
-      </c>
-      <c r="C40">
-        <v>78632</v>
-      </c>
-      <c r="D40">
-        <v>101304</v>
+        <v>47</v>
+      </c>
+      <c r="B40" s="1">
+        <v>197670.85798816569</v>
+      </c>
+      <c r="C40" s="1">
+        <v>95667.33466933867</v>
+      </c>
+      <c r="D40" s="1">
+        <v>128865.74819917411</v>
       </c>
     </row>
   </sheetData>
@@ -2006,6 +2008,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c78a888a-83d8-49bb-8890-6eb97e8a3c0e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100763DCA751E988E49B18D7A5F3E2E0A59" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5b021fe13dcae56d252e7321283a3f3b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd" xmlns:ns3="c78a888a-83d8-49bb-8890-6eb97e8a3c0e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d73ac3668dfd0d4084037886131f3a8" ns2:_="" ns3:_="">
     <xsd:import namespace="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
@@ -2248,17 +2261,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c78a888a-83d8-49bb-8890-6eb97e8a3c0e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2269,6 +2271,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A3ADF35-F119-4BE6-85A8-2E5C6C3A1AE7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c78a888a-83d8-49bb-8890-6eb97e8a3c0e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1C2D98D-4316-42A5-A479-7A098215D7A8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2287,27 +2306,16 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A3ADF35-F119-4BE6-85A8-2E5C6C3A1AE7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c78a888a-83d8-49bb-8890-6eb97e8a3c0e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B31F663-6144-4024-83F4-0C35A9D0D635}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{fd60f3b8-f236-4830-aecc-da0a7fc54679}" enabled="1" method="Standard" siteId="{76f33c20-5979-4408-adf7-8b3c4be95e52}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>